--- a/data-manipulation-scripts/sheets-cleanup/sheets/MAGNETO COMPLETO.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/MAGNETO COMPLETO.xlsx
@@ -92,7 +92,7 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -359,7 +359,9 @@
       <c r="C2" s="4">
         <v>2.0</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="5">
+        <v>270.0</v>
+      </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
